--- a/HPB_Templates/SystemicTherapyDefinition_export.xlsx
+++ b/HPB_Templates/SystemicTherapyDefinition_export.xlsx
@@ -321,7 +321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="8.710000000000001" customWidth="1" style="2" min="1" max="1"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Gemcitabine plus nab-paclitaxel</t>
+          <t>gem + nab-paclitaxel</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -1157,9 +1157,51 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="2"/>
-    <row r="46" ht="15.75" customHeight="1" s="2"/>
-    <row r="47" ht="15.75" customHeight="1" s="2"/>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>NALIRIFOX</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Liposomal irinotecan, oxaliplatin, fluorouracil and folinic acid; first-line combination chemotherapy for metastatic pancreatic cancer</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>Other regimen not in the list (name it in the note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>gem mono</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>Gemcitabine monotherapy: the regimen for patients too frail for combination chemotherapy (the drug itself is "Gemcitabine")</t>
+        </is>
+      </c>
+    </row>
     <row r="48" ht="15.75" customHeight="1" s="2"/>
     <row r="49" ht="15.75" customHeight="1" s="2"/>
     <row r="50" ht="15.75" customHeight="1" s="2"/>
